--- a/results/job_matches_2026-04-26.xlsx
+++ b/results/job_matches_2026-04-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,85 +478,85 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>13.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b29c302cd453d25</t>
+          <t>https://www.indeed.com/viewjob?jk=58e46008e082a2c5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Database Engineer I</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Webster, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b68f7381cd9ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Software Engineer (Python)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rocky Mountain Elk Foundation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9015f8bca6247309</t>
+          <t>https://www.indeed.com/viewjob?jk=6325226098b53d8c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Naphcare, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8dec88435b36ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=50e1c69114e7cd26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nimble</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,119 +636,119 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=468bb000278c0677</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe726b1c2405926</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer- Fulfillment Team</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
+          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Guidewire</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8debac1e37803644</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Azure Data Architect</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CENTSTONE SERVICES LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hazlet, NJ, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
+          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,49 +776,49 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e46008e082a2c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Database Engineer I</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Webster, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Python)</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,15 +828,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6325226098b53d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Platform Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Naphcare, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e1c69114e7cd26</t>
+          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe726b1c2405926</t>
+          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer, Testing</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
+          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
+          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RailPros</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
+          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8debac1e37803644</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
+          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
+          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
+          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Google Cloud Platform, Vertex AI, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90f877954706efc9</t>
+          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
+          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Developer - AI</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>API Architect (Python)</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf022575a6c3cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Security Backend Engineer (Python)</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
+          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
+          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,229 +1616,229 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
+          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
+          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
+          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
+          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1847,21 +1847,3801 @@
         </is>
       </c>
       <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19cc1f4c2f73710b</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=969c8212168e8da2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a83061861f3e145</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=456535dd8b6016df</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07d37ab970ee1792</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caf64dd5f6c867c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c287037b4d66cea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86ddf49312cd2b0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05e846407f299d79</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4dbf2c6e8f929e74</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a09942bef057dc62</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fc55450909faf35</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7cb5fc6346c3d99</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f12e1db4c4d6d0ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e15a06584c3fe14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5103f3c192b54c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ff03a970a3566b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=626ffde9f1440a06</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f309595dac79efc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df0d970d9350d9a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=032c68d2bf31c0c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2272ed9463605fa5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bb0f41c56b52b6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1aef3f110a1972d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30f1979cd3ebcf73</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37c9bd8ccaa619f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22b30a5495956c21</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3deab56cb2edcfb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0fea591d73cc5cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4c712155f24d1a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3582c84c00c1b33</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=823618527ca4fb59</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d01dc174ca2ecf02</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b779622beca8e90f</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31c2fd523da9cec1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ad8b751eb7cf811</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ab1e0d9d0f377db</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80d935e6216a5d75</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d74952dbd137d52</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=600c5da92e81865a</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aee3b77b4f97cd01</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4510a0b8ce2a86dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a691a615121eb26</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a10ad1526a079c12</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=107983cc41e10757</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f61d683e9f1fc7d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec3a986934b22e25</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e743c51d2f3262d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26bd0fddf517eda9</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aeeabafbbeeac857</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd38a15864b38a38</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5341518d5fa7303d</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=add2513583b97758</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58e7e9987f29d130</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c99a41f820d8520d</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=961f54ac084d96c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a964833d7f362fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50bf49411126b877</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46ae3873bcc7493f</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3591db78aabc9d31</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad4a9263528190b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6503a6f594d6cb40</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3477c37d3b1d012e</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a46bd2ae07b31e06</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61b2f90e644742c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a169a5687aa46867</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a4aa7976996ca43</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af351b4140df825f</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2fa67c9009bba45</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4a6b561734ab4cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=652eeaac9bdbf7d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ef653ea6a206692</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4c5a1dcf01389f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47e073986ad3d626</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acf400d2cc22b3f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1598c9bab3bf442f</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee28e2ffc7acf08f</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6bfbd2b3524c7712</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e7dfec8721b3485</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fee66dd67e651a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1346911bb1afeece</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34e3b9eb79fb9e4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5151d5e9aa17e5d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>FastAPI</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Google Cloud Platform, Vertex AI, MySQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90f877954706efc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Java CI/CD Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Java CI/CD Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>API Architect (Python)</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
         <v>10.4</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Spark, Snowflake, Data Modeling, Tableau, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=07f643dd409c7140</t>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cf022575a6c3cfb</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Security Backend Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Java SDK / Library Developer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-26.xlsx
+++ b/results/job_matches_2026-04-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Database Engineer I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Webster, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,34 +486,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e46008e082a2c5</t>
+          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Database Engineer I</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Webster, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
+          <t>https://www.indeed.com/viewjob?jk=58e46008e082a2c5</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe726b1c2405926</t>
+          <t>https://www.indeed.com/viewjob?jk=b563dee50b08e5a4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe726b1c2405926</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,15 +688,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8debac1e37803644</t>
+          <t>https://www.indeed.com/viewjob?jk=0d88c948e0a02d22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
+          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
+          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=8debac1e37803644</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=f510815207394b27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
+          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
+          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
+          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
+          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
+          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
+          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
+          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
+          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
+          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
+          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
+          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
+          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
+          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
+          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
+          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
+          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
+          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
+          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
+          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
+          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
+          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
+          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
+          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
+          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
+          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
+          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
+          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
+          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cc1f4c2f73710b</t>
+          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=969c8212168e8da2</t>
+          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a83061861f3e145</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=456535dd8b6016df</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d37ab970ee1792</t>
+          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf64dd5f6c867c6</t>
+          <t>https://www.indeed.com/viewjob?jk=19cc1f4c2f73710b</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c287037b4d66cea0</t>
+          <t>https://www.indeed.com/viewjob?jk=969c8212168e8da2</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ddf49312cd2b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a83061861f3e145</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e846407f299d79</t>
+          <t>https://www.indeed.com/viewjob?jk=456535dd8b6016df</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dbf2c6e8f929e74</t>
+          <t>https://www.indeed.com/viewjob?jk=07d37ab970ee1792</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a09942bef057dc62</t>
+          <t>https://www.indeed.com/viewjob?jk=caf64dd5f6c867c6</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc55450909faf35</t>
+          <t>https://www.indeed.com/viewjob?jk=c287037b4d66cea0</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7cb5fc6346c3d99</t>
+          <t>https://www.indeed.com/viewjob?jk=86ddf49312cd2b0f</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f12e1db4c4d6d0ac</t>
+          <t>https://www.indeed.com/viewjob?jk=05e846407f299d79</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e15a06584c3fe14</t>
+          <t>https://www.indeed.com/viewjob?jk=4dbf2c6e8f929e74</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5103f3c192b54c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a09942bef057dc62</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff03a970a3566b6</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc55450909faf35</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626ffde9f1440a06</t>
+          <t>https://www.indeed.com/viewjob?jk=b7cb5fc6346c3d99</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f309595dac79efc3</t>
+          <t>https://www.indeed.com/viewjob?jk=f12e1db4c4d6d0ac</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df0d970d9350d9a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e15a06584c3fe14</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032c68d2bf31c0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e5103f3c192b54c5</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2272ed9463605fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff03a970a3566b6</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bb0f41c56b52b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=626ffde9f1440a06</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aef3f110a1972d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f309595dac79efc3</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f1979cd3ebcf73</t>
+          <t>https://www.indeed.com/viewjob?jk=df0d970d9350d9a2</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37c9bd8ccaa619f3</t>
+          <t>https://www.indeed.com/viewjob?jk=032c68d2bf31c0c1</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b30a5495956c21</t>
+          <t>https://www.indeed.com/viewjob?jk=2272ed9463605fa5</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3deab56cb2edcfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=0bb0f41c56b52b6c</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fea591d73cc5cb</t>
+          <t>https://www.indeed.com/viewjob?jk=1aef3f110a1972d6</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c712155f24d1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=30f1979cd3ebcf73</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3582c84c00c1b33</t>
+          <t>https://www.indeed.com/viewjob?jk=37c9bd8ccaa619f3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AI Engineer Senior Consultant</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823618527ca4fb59</t>
+          <t>https://www.indeed.com/viewjob?jk=22b30a5495956c21</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01dc174ca2ecf02</t>
+          <t>https://www.indeed.com/viewjob?jk=3deab56cb2edcfb9</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b779622beca8e90f</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fea591d73cc5cb</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c2fd523da9cec1</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c712155f24d1a6</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad8b751eb7cf811</t>
+          <t>https://www.indeed.com/viewjob?jk=c3582c84c00c1b33</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>AI Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab1e0d9d0f377db</t>
+          <t>https://www.indeed.com/viewjob?jk=823618527ca4fb59</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI Engineer Senior Consultant</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d935e6216a5d75</t>
+          <t>https://www.indeed.com/viewjob?jk=d01dc174ca2ecf02</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d74952dbd137d52</t>
+          <t>https://www.indeed.com/viewjob?jk=b779622beca8e90f</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600c5da92e81865a</t>
+          <t>https://www.indeed.com/viewjob?jk=31c2fd523da9cec1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AI Engineer Senior Consultant</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee3b77b4f97cd01</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad8b751eb7cf811</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4510a0b8ce2a86dd</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab1e0d9d0f377db</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>AI Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a691a615121eb26</t>
+          <t>https://www.indeed.com/viewjob?jk=80d935e6216a5d75</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10ad1526a079c12</t>
+          <t>https://www.indeed.com/viewjob?jk=1d74952dbd137d52</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Engineer Senior Consultant</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,14 +4066,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=107983cc41e10757</t>
+          <t>https://www.indeed.com/viewjob?jk=600c5da92e81865a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>AI Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61d683e9f1fc7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=aee3b77b4f97cd01</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3a986934b22e25</t>
+          <t>https://www.indeed.com/viewjob?jk=4510a0b8ce2a86dd</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e743c51d2f3262d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a691a615121eb26</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI Engineer Senior Consultant</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26bd0fddf517eda9</t>
+          <t>https://www.indeed.com/viewjob?jk=a10ad1526a079c12</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,14 +4241,14 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeeabafbbeeac857</t>
+          <t>https://www.indeed.com/viewjob?jk=107983cc41e10757</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AI Engineer Senior Consultant</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,14 +4276,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd38a15864b38a38</t>
+          <t>https://www.indeed.com/viewjob?jk=f61d683e9f1fc7d3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI Engineer Senior Consultant</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5341518d5fa7303d</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3a986934b22e25</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AI Engineer Senior Consultant</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add2513583b97758</t>
+          <t>https://www.indeed.com/viewjob?jk=e743c51d2f3262d5</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e7e9987f29d130</t>
+          <t>https://www.indeed.com/viewjob?jk=26bd0fddf517eda9</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99a41f820d8520d</t>
+          <t>https://www.indeed.com/viewjob?jk=aeeabafbbeeac857</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961f54ac084d96c1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd38a15864b38a38</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a964833d7f362fe</t>
+          <t>https://www.indeed.com/viewjob?jk=5341518d5fa7303d</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50bf49411126b877</t>
+          <t>https://www.indeed.com/viewjob?jk=add2513583b97758</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ae3873bcc7493f</t>
+          <t>https://www.indeed.com/viewjob?jk=58e7e9987f29d130</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3591db78aabc9d31</t>
+          <t>https://www.indeed.com/viewjob?jk=c99a41f820d8520d</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a9263528190b8</t>
+          <t>https://www.indeed.com/viewjob?jk=961f54ac084d96c1</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6503a6f594d6cb40</t>
+          <t>https://www.indeed.com/viewjob?jk=5a964833d7f362fe</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3477c37d3b1d012e</t>
+          <t>https://www.indeed.com/viewjob?jk=50bf49411126b877</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a46bd2ae07b31e06</t>
+          <t>https://www.indeed.com/viewjob?jk=46ae3873bcc7493f</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61b2f90e644742c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3591db78aabc9d31</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a169a5687aa46867</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a9263528190b8</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a4aa7976996ca43</t>
+          <t>https://www.indeed.com/viewjob?jk=6503a6f594d6cb40</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af351b4140df825f</t>
+          <t>https://www.indeed.com/viewjob?jk=3477c37d3b1d012e</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2fa67c9009bba45</t>
+          <t>https://www.indeed.com/viewjob?jk=a46bd2ae07b31e06</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a6b561734ab4cf</t>
+          <t>https://www.indeed.com/viewjob?jk=61b2f90e644742c6</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652eeaac9bdbf7d5</t>
+          <t>https://www.indeed.com/viewjob?jk=a169a5687aa46867</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef653ea6a206692</t>
+          <t>https://www.indeed.com/viewjob?jk=6a4aa7976996ca43</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c5a1dcf01389f2</t>
+          <t>https://www.indeed.com/viewjob?jk=af351b4140df825f</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e073986ad3d626</t>
+          <t>https://www.indeed.com/viewjob?jk=b2fa67c9009bba45</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acf400d2cc22b3f6</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a6b561734ab4cf</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1598c9bab3bf442f</t>
+          <t>https://www.indeed.com/viewjob?jk=652eeaac9bdbf7d5</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee28e2ffc7acf08f</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef653ea6a206692</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbd2b3524c7712</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c5a1dcf01389f2</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e7dfec8721b3485</t>
+          <t>https://www.indeed.com/viewjob?jk=47e073986ad3d626</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fee66dd67e651a7</t>
+          <t>https://www.indeed.com/viewjob?jk=acf400d2cc22b3f6</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1346911bb1afeece</t>
+          <t>https://www.indeed.com/viewjob?jk=1598c9bab3bf442f</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e3b9eb79fb9e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee28e2ffc7acf08f</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5151d5e9aa17e5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbd2b3524c7712</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>AI Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Google Cloud Platform, Vertex AI, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90f877954706efc9</t>
+          <t>https://www.indeed.com/viewjob?jk=4e7dfec8721b3485</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>AI Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fee66dd67e651a7</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>AI Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,32 +5501,32 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
+          <t>https://www.indeed.com/viewjob?jk=1346911bb1afeece</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>API Architect (Python)</t>
+          <t>AI Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,32 +5536,32 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf022575a6c3cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=34e3b9eb79fb9e4f</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Security Backend Engineer (Python)</t>
+          <t>AI Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,14 +5571,14 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
+          <t>https://www.indeed.com/viewjob?jk=5151d5e9aa17e5d5</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5588,15 +5588,15 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Google Cloud Platform, Vertex AI, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,42 +5606,182 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
+          <t>https://www.indeed.com/viewjob?jk=90f877954706efc9</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, MLOps, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bcc4b728c62daf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Security Backend Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
           <t>Java SDK / Library Developer</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>GA, US USA</t>
         </is>
       </c>
-      <c r="D149" t="n">
+      <c r="D152" t="n">
         <v>10.4</v>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>API Architect (Python)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cf022575a6c3cfb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-26.xlsx
+++ b/results/job_matches_2026-04-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
+          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
+          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
+          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
+          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
+          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
+          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
+          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
+          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
+          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
+          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
+          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
+          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
+          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
+          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
+          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
+          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
+          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
+          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
+          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
+          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
+          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
+          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
+          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
+          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
+          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
+          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
+          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
+          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Security Backend Engineer (Python)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2267,11 +2267,11 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,15 +2298,15 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,112 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Security Backend Engineer (Python)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Java SDK / Library Developer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-26.xlsx
+++ b/results/job_matches_2026-04-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
+          <t>https://www.indeed.com/viewjob?jk=869dab0c8225dd66</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,42 +513,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
+          <t>https://www.indeed.com/viewjob?jk=44a6b10cd1d80de1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
+          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,182 +591,182 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
+          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b0bf6f67742d88</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
+          <t>https://www.indeed.com/viewjob?jk=84bea4b7a07e62e7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d1fb002ebc8873</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
+          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5f43c9e792ef678e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
+          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
+          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
+          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
+          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
+          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
+          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
+          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
+          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
+          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
+          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
+          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
+          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
+          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
+          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
+          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
+          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
+          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
+          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
+          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
+          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
+          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
+          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
+          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
+          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
+          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Security Backend Engineer (Python)</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,40 +2281,355 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
+          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Java CI/CD Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92f3943a0fdcede7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Java CI/CD Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f6848655c24fa10</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Java CI/CD Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Security Backend Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>TX, US USA</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D63" t="n">
         <v>10.4</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
         </is>

--- a/results/job_matches_2026-04-26.xlsx
+++ b/results/job_matches_2026-04-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=869dab0c8225dd66</t>
+          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Platform Engineer</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,42 +513,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44a6b10cd1d80de1</t>
+          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
+          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d1fb002ebc8873</t>
+          <t>https://www.indeed.com/viewjob?jk=5f43c9e792ef678e</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -701,19 +701,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f43c9e792ef678e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
+          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
+          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
+          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
+          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
+          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
+          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
+          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
+          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
+          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
+          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
+          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
+          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
+          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
+          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
+          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
+          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
+          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
+          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
+          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
+          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
+          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
+          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
+          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
+          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
+          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
+          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
+          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
+          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
+          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
+          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Security Backend Engineer (Python)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2455,181 +2455,6 @@
         </is>
       </c>
       <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Java CI/CD Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92f3943a0fdcede7</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Java CI/CD Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f6848655c24fa10</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Java CI/CD Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Security Backend Engineer (Python)</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
         </is>

--- a/results/job_matches_2026-04-26.xlsx
+++ b/results/job_matches_2026-04-26.xlsx
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b0bf6f67742d88</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=84bea4b7a07e62e7</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b0bf6f67742d88</t>
+          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
         </is>
       </c>
     </row>
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bea4b7a07e62e7</t>
+          <t>https://www.indeed.com/viewjob?jk=5f43c9e792ef678e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f43c9e792ef678e</t>
+          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-26.xlsx
+++ b/results/job_matches_2026-04-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b0bf6f67742d88</t>
+          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bea4b7a07e62e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -596,19 +596,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f43c9e792ef678e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
+          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
+          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
+          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
+          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
+          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
+          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
+          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
+          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
+          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
+          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
+          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
+          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
+          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
+          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
+          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
+          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
+          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
+          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
+          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
+          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
+          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
+          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
+          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
+          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
+          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
+          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
+          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
+          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
+          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
+          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Security Backend Engineer (Python)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2350,111 +2350,6 @@
         </is>
       </c>
       <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Java CI/CD Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Security Backend Engineer (Python)</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
         </is>

--- a/results/job_matches_2026-04-26.xlsx
+++ b/results/job_matches_2026-04-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
+          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
+          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
+          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
+          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
+          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
+          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
+          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
+          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
+          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
+          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
+          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
+          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
+          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
+          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
+          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
+          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
+          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
+          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
+          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
+          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
+          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
+          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
+          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
+          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
+          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
+          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
+          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
+          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Security Backend Engineer (Python)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,112 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Java CI/CD Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Security Backend Engineer (Python)</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-26.xlsx
+++ b/results/job_matches_2026-04-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Java Application Support Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.8</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
+          <t>https://www.indeed.com/viewjob?jk=9deace07d50ab229</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,32 +513,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
+          <t>https://www.indeed.com/viewjob?jk=7fec72ec0a2829cf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,15 +548,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ff70697f7c7e8d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
+          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
+          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
+          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
+          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
+          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
+          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
+          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
+          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
+          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
+          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
+          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
+          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
+          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
+          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
+          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
+          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
+          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
+          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
+          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
+          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
+          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
+          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
+          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
+          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
+          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
+          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
+          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
+          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,40 +2211,145 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
+          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Security Backend Engineer (Python)</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>GA, US USA</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D55" t="n">
         <v>10.4</v>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
         </is>

--- a/results/job_matches_2026-04-26.xlsx
+++ b/results/job_matches_2026-04-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fec72ec0a2829cf</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ff70697f7c7e8d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ff70697f7c7e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
+          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,24 +626,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
+          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
+          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
+          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
+          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
+          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
+          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
+          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
+          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
+          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
+          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
+          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
+          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
+          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
+          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
+          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
+          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
+          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
+          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
+          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
+          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
+          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
+          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
+          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
+          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
+          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
+          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
+          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
+          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
+          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Security Backend Engineer (Python)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2315,41 +2315,6 @@
         </is>
       </c>
       <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Security Backend Engineer (Python)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
         </is>

--- a/results/job_matches_2026-04-26.xlsx
+++ b/results/job_matches_2026-04-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
+          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
+          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
+          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
+          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
+          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
+          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
+          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
+          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
+          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
+          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
+          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
+          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
+          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
+          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
+          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
+          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
+          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
+          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
+          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
+          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
+          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
+          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
+          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
+          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
+          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
+          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
+          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,40 +2281,75 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
+          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Security Backend Engineer (Python)</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>GA, US USA</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D55" t="n">
         <v>10.4</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
         </is>

--- a/results/job_matches_2026-04-26.xlsx
+++ b/results/job_matches_2026-04-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Java Application Support Analyst</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>14.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9deace07d50ab229</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c0dbf66c41408a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ff70697f7c7e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
+          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,24 +591,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
+          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,69 +626,69 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33cdbb1ad6ddbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
+          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
+          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
+          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
+          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
+          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
+          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
+          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
+          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
+          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
+          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
+          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
+          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
+          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
+          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
+          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
+          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
+          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
+          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
+          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
+          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
+          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
+          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
+          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
+          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
+          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
+          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
+          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
+          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
+          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>Security Backend Engineer (Python)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2315,41 +2315,6 @@
         </is>
       </c>
       <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Security Backend Engineer (Python)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
         </is>

--- a/results/job_matches_2026-04-26.xlsx
+++ b/results/job_matches_2026-04-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
+          <t>https://www.indeed.com/viewjob?jk=d695750f2c0009c2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
+          <t>https://www.indeed.com/viewjob?jk=d25e680dbcf02691</t>
         </is>
       </c>
     </row>
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Data Engineer - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
+          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be55de12b97a3eea</t>
+          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=689abcfa7454712d</t>
+          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d306ae5de331fba4</t>
+          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade2e601264058d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eade2476ce324cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4e553f943c75c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3832af338c1736</t>
+          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08027bdb175fef3</t>
+          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a357b890dc2091c</t>
+          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af99ad9ba959c44</t>
+          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d427da59ac53cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3823a2d9a71db9e</t>
+          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07a9c469cd6ed00</t>
+          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154af2613a067aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=781222d31a9425c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23cfafb9e7aeee9d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8b189f367ac88d</t>
+          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d59292d009da37</t>
+          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c629ed371d7a40af</t>
+          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54a426723eeee3d</t>
+          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac26d294464ef290</t>
+          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ea21628ff33f06</t>
+          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=680eaa5fbea3d780</t>
+          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125c1aae9fbfeaad</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a477e31fb8c4de</t>
+          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fd3156e00bc73a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979391319238d1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3f64995c46ffb5</t>
+          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7badd7798c756b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e30745da92b5fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2b120f8275973c</t>
+          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74b4479553e40358</t>
+          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2edd246d5ca2e29</t>
+          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d19fead7d440f</t>
+          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b081536fdb9e24</t>
+          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a8014e5a2c6189</t>
+          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07eec52616843afa</t>
+          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08de63a1b1380df</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102145cd98b4dde9</t>
+          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1f20dfcff1b16e</t>
+          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6430d64ac9dd2912</t>
+          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86100b664a2f72c3</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5173daca446e4893</t>
+          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf7a3c858711ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,87 +2236,52 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f279da09c96314</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ca9d67a5eb74a0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Project Delivery Senior Analyst</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186cf3142f717645</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Security Backend Engineer (Python)</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
+          <t>https://www.indeed.com/viewjob?jk=01f0b4141850808c</t>
         </is>
       </c>
     </row>
